--- a/EKG_Kalite_Yönetim_Sistemi/09_Risk Azaltma ve PFMEA/01_RR1 - PFMEA ve Müşteri Puanlama Kuralları/EKG-PRJ-FRM-03_aile_ve_urune_ozel_pfmea_sablonu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/09_Risk Azaltma ve PFMEA/01_RR1 - PFMEA ve Müşteri Puanlama Kuralları/EKG-PRJ-FRM-03_aile_ve_urune_ozel_pfmea_sablonu.xlsx
@@ -851,7 +851,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-03&amp;C&amp;"Arial,Regular"&amp;11Aile ve Ürüne Özel PFMEA Şablonu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 22.09.2026
+Revizyon nedeni: Aile ve ürün PFMEA analizleri korundu; aksiyon/kanıt aynı Risk ID ile ayrı aksiyon sayfasına taşındı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1046,7 +1047,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-03&amp;C&amp;"Arial,Regular"&amp;11Aile ve Ürüne Özel PFMEA Şablonu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 22.09.2026
+Revizyon nedeni: Aile ve ürün PFMEA analizleri korundu; aksiyon/kanıt aynı Risk ID ile ayrı aksiyon sayfasına taşındı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1276,7 +1278,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-03&amp;C&amp;"Arial,Regular"&amp;11Aile ve Ürüne Özel PFMEA Şablonu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 22.09.2026
+Revizyon nedeni: Aile ve ürün PFMEA analizleri korundu; aksiyon/kanıt aynı Risk ID ile ayrı aksiyon sayfasına taşındı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>